--- a/03.商業計畫書BootCamp/創業綻放計畫  一對一業師輔導媒合結果公告(即時更新).xlsx
+++ b/03.商業計畫書BootCamp/創業綻放計畫  一對一業師輔導媒合結果公告(即時更新).xlsx
@@ -309,13 +309,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0002")</f>
         <v>A0002</v>
       </c>
-      <c r="B2" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
+      <c r="B2" s="3"/>
       <c r="C2" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"115/03/03 15:00")</f>
-        <v>115/03/03 15:00</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"115/03/09 14:06")</f>
+        <v>115/03/09 14:06</v>
       </c>
     </row>
     <row r="3">
@@ -500,8 +497,8 @@
         <v>A0135</v>
       </c>
       <c r="B19" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"國立陽明交通大學產業加速器暨專利開發策略中心")</f>
+        <v>國立陽明交通大學產業加速器暨專利開發策略中心</v>
       </c>
       <c r="C19" s="3"/>
     </row>
@@ -665,8 +662,8 @@
         <v>A0259</v>
       </c>
       <c r="B34" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"國立陽明交通大學產業加速器暨專利開發策略中心")</f>
+        <v>國立陽明交通大學產業加速器暨專利開發策略中心</v>
       </c>
       <c r="C34" s="3"/>
     </row>
@@ -731,8 +728,8 @@
         <v>A0298</v>
       </c>
       <c r="B40" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"購威經濟股份有限公司(智慧高軟)")</f>
+        <v>購威經濟股份有限公司(智慧高軟)</v>
       </c>
       <c r="C40" s="3"/>
     </row>
@@ -752,10 +749,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0300")</f>
         <v>A0300</v>
       </c>
-      <c r="B42" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
+      <c r="B42" s="3"/>
       <c r="C42" s="3"/>
     </row>
     <row r="43">
@@ -775,8 +769,8 @@
         <v>A0330</v>
       </c>
       <c r="B44" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"StarFab (豪覓管理顧問股份有限公司)")</f>
+        <v>StarFab (豪覓管理顧問股份有限公司)</v>
       </c>
       <c r="C44" s="3"/>
     </row>
@@ -808,8 +802,8 @@
         <v>A0350</v>
       </c>
       <c r="B47" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
+        <v>資誠聯合會計師事務所</v>
       </c>
       <c r="C47" s="3"/>
     </row>
@@ -885,8 +879,8 @@
         <v>A0408</v>
       </c>
       <c r="B54" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
+        <v>比翼生醫</v>
       </c>
       <c r="C54" s="3"/>
     </row>
@@ -940,8 +934,8 @@
         <v>A0441</v>
       </c>
       <c r="B59" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"StarFab (豪覓管理顧問股份有限公司)")</f>
+        <v>StarFab (豪覓管理顧問股份有限公司)</v>
       </c>
       <c r="C59" s="3"/>
     </row>
@@ -1072,8 +1066,8 @@
         <v>A0528</v>
       </c>
       <c r="B71" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"StarFab (豪覓管理顧問股份有限公司)")</f>
+        <v>StarFab (豪覓管理顧問股份有限公司)</v>
       </c>
       <c r="C71" s="3"/>
     </row>
@@ -1116,8 +1110,8 @@
         <v>A0542</v>
       </c>
       <c r="B75" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
+        <v>好食好事加速器</v>
       </c>
       <c r="C75" s="3"/>
     </row>
@@ -1127,8 +1121,8 @@
         <v>A0551</v>
       </c>
       <c r="B76" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"扶田資本股份有限公司")</f>
+        <v>扶田資本股份有限公司</v>
       </c>
       <c r="C76" s="3"/>
     </row>
@@ -1138,8 +1132,8 @@
         <v>A0565</v>
       </c>
       <c r="B77" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
+        <v>比翼生醫</v>
       </c>
       <c r="C77" s="3"/>
     </row>
@@ -1182,8 +1176,8 @@
         <v>A0582</v>
       </c>
       <c r="B81" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
       </c>
       <c r="C81" s="3"/>
     </row>
@@ -1204,8 +1198,8 @@
         <v>A0586</v>
       </c>
       <c r="B83" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Garage+")</f>
+        <v>Garage+</v>
       </c>
       <c r="C83" s="3"/>
     </row>
@@ -1281,8 +1275,8 @@
         <v>A0622</v>
       </c>
       <c r="B90" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"生物技術開發中心(南港生技育成中心)")</f>
+        <v>生物技術開發中心(南港生技育成中心)</v>
       </c>
       <c r="C90" s="3"/>
     </row>
@@ -1324,10 +1318,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0634")</f>
         <v>A0634</v>
       </c>
-      <c r="B94" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
+      <c r="B94" s="3"/>
       <c r="C94" s="3"/>
     </row>
     <row r="95">
@@ -1380,8 +1371,8 @@
         <v>A0651</v>
       </c>
       <c r="B99" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"扶田資本股份有限公司")</f>
+        <v>扶田資本股份有限公司</v>
       </c>
       <c r="C99" s="3"/>
     </row>
@@ -1420,206 +1411,203 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0667")</f>
-        <v>A0667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0674")</f>
+        <v>A0674</v>
       </c>
       <c r="B103" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
-        <v>好食好事加速器</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
+        <v>比翼生醫</v>
       </c>
       <c r="C103" s="3"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0674")</f>
-        <v>A0674</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0677")</f>
+        <v>A0677</v>
       </c>
       <c r="B104" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資育股份有限公司")</f>
+        <v>資育股份有限公司</v>
+      </c>
+      <c r="C104" s="3"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0686")</f>
+        <v>A0686</v>
+      </c>
+      <c r="B105" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C105" s="3"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0687")</f>
+        <v>A0687</v>
+      </c>
+      <c r="B106" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
+        <v>尚未報名/媒合中</v>
+      </c>
+      <c r="C106" s="3"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0693")</f>
+        <v>A0693</v>
+      </c>
+      <c r="B107" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"StarFab (豪覓管理顧問股份有限公司)")</f>
+        <v>StarFab (豪覓管理顧問股份有限公司)</v>
+      </c>
+      <c r="C107" s="3"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0694")</f>
+        <v>A0694</v>
+      </c>
+      <c r="B108" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
+        <v>尚未報名/媒合中</v>
+      </c>
+      <c r="C108" s="3"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0695")</f>
+        <v>A0695</v>
+      </c>
+      <c r="B109" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
+        <v>資誠聯合會計師事務所</v>
+      </c>
+      <c r="C109" s="3"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0702")</f>
+        <v>A0702</v>
+      </c>
+      <c r="B110" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Garage+")</f>
+        <v>Garage+</v>
+      </c>
+      <c r="C110" s="3"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0708")</f>
+        <v>A0708</v>
+      </c>
+      <c r="B111" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C111" s="3"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0716")</f>
+        <v>A0716</v>
+      </c>
+      <c r="B112" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C112" s="3"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0722")</f>
+        <v>A0722</v>
+      </c>
+      <c r="B113" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C113" s="3"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0727")</f>
+        <v>A0727</v>
+      </c>
+      <c r="B114" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
+        <v>資誠聯合會計師事務所</v>
+      </c>
+      <c r="C114" s="3"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0745")</f>
+        <v>A0745</v>
+      </c>
+      <c r="B115" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
         <v>比翼生醫</v>
       </c>
-      <c r="C104" s="3"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0677")</f>
-        <v>A0677</v>
-      </c>
-      <c r="B105" s="3" t="str">
+      <c r="C115" s="3"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0749")</f>
+        <v>A0749</v>
+      </c>
+      <c r="B116" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"活水影響力投資")</f>
+        <v>活水影響力投資</v>
+      </c>
+      <c r="C116" s="3"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0755")</f>
+        <v>A0755</v>
+      </c>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0756")</f>
+        <v>A0756</v>
+      </c>
+      <c r="B118" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"扶田資本股份有限公司")</f>
+        <v>扶田資本股份有限公司</v>
+      </c>
+      <c r="C118" s="3"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0770")</f>
+        <v>A0770</v>
+      </c>
+      <c r="B119" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資育股份有限公司")</f>
         <v>資育股份有限公司</v>
       </c>
-      <c r="C105" s="3"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0686")</f>
-        <v>A0686</v>
-      </c>
-      <c r="B106" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
-        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
-      </c>
-      <c r="C106" s="3"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0687")</f>
-        <v>A0687</v>
-      </c>
-      <c r="B107" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C107" s="3"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0693")</f>
-        <v>A0693</v>
-      </c>
-      <c r="B108" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"StarFab (豪覓管理顧問股份有限公司)")</f>
-        <v>StarFab (豪覓管理顧問股份有限公司)</v>
-      </c>
-      <c r="C108" s="3"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0694")</f>
-        <v>A0694</v>
-      </c>
-      <c r="B109" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C109" s="3"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0695")</f>
-        <v>A0695</v>
-      </c>
-      <c r="B110" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C110" s="3"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0702")</f>
-        <v>A0702</v>
-      </c>
-      <c r="B111" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Garage+")</f>
-        <v>Garage+</v>
-      </c>
-      <c r="C111" s="3"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0708")</f>
-        <v>A0708</v>
-      </c>
-      <c r="B112" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
-        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
-      </c>
-      <c r="C112" s="3"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0716")</f>
-        <v>A0716</v>
-      </c>
-      <c r="B113" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
-        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
-      </c>
-      <c r="C113" s="3"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0722")</f>
-        <v>A0722</v>
-      </c>
-      <c r="B114" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C114" s="3"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0727")</f>
-        <v>A0727</v>
-      </c>
-      <c r="B115" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
-        <v>資誠聯合會計師事務所</v>
-      </c>
-      <c r="C115" s="3"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0745")</f>
-        <v>A0745</v>
-      </c>
-      <c r="B116" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
-        <v>比翼生醫</v>
-      </c>
-      <c r="C116" s="3"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0749")</f>
-        <v>A0749</v>
-      </c>
-      <c r="B117" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"活水影響力投資")</f>
-        <v>活水影響力投資</v>
-      </c>
-      <c r="C117" s="3"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0755")</f>
-        <v>A0755</v>
-      </c>
-      <c r="B118" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C118" s="3"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0756")</f>
-        <v>A0756</v>
-      </c>
-      <c r="B119" s="3" t="str">
+      <c r="C119" s="3"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0773")</f>
+        <v>A0773</v>
+      </c>
+      <c r="B120" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"扶田資本股份有限公司")</f>
         <v>扶田資本股份有限公司</v>
       </c>
-      <c r="C119" s="3"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0770")</f>
-        <v>A0770</v>
-      </c>
-      <c r="B120" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
       <c r="C120" s="3"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0773")</f>
-        <v>A0773</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0775")</f>
+        <v>A0775</v>
       </c>
       <c r="B121" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"扶田資本股份有限公司")</f>
@@ -1629,173 +1617,173 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0775")</f>
-        <v>A0775</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0777")</f>
+        <v>A0777</v>
       </c>
       <c r="B122" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"扶田資本股份有限公司")</f>
-        <v>扶田資本股份有限公司</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
+        <v>聯合創新加速器</v>
       </c>
       <c r="C122" s="3"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0777")</f>
-        <v>A0777</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0787")</f>
+        <v>A0787</v>
       </c>
       <c r="B123" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
-        <v>聯合創新加速器</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"購威經濟股份有限公司(智慧高軟)")</f>
+        <v>購威經濟股份有限公司(智慧高軟)</v>
       </c>
       <c r="C123" s="3"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0787")</f>
-        <v>A0787</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0799")</f>
+        <v>A0799</v>
       </c>
       <c r="B124" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"購威經濟股份有限公司(智慧高軟)")</f>
-        <v>購威經濟股份有限公司(智慧高軟)</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
+        <v>比翼生醫</v>
       </c>
       <c r="C124" s="3"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0799")</f>
-        <v>A0799</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0800")</f>
+        <v>A0800</v>
       </c>
       <c r="B125" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
-        <v>比翼生醫</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資育股份有限公司")</f>
+        <v>資育股份有限公司</v>
       </c>
       <c r="C125" s="3"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0800")</f>
-        <v>A0800</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0801")</f>
+        <v>A0801</v>
       </c>
       <c r="B126" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Muse Builder")</f>
+        <v>Muse Builder</v>
+      </c>
+      <c r="C126" s="3"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0808")</f>
+        <v>A0808</v>
+      </c>
+      <c r="B127" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C127" s="3"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0814")</f>
+        <v>A0814</v>
+      </c>
+      <c r="B128" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C128" s="3"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0815")</f>
+        <v>A0815</v>
+      </c>
+      <c r="B129" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
+        <v>好食好事加速器</v>
+      </c>
+      <c r="C129" s="3"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0833")</f>
+        <v>A0833</v>
+      </c>
+      <c r="B130" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"StarFab (豪覓管理顧問股份有限公司)")</f>
+        <v>StarFab (豪覓管理顧問股份有限公司)</v>
+      </c>
+      <c r="C130" s="3"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0838")</f>
+        <v>A0838</v>
+      </c>
+      <c r="B131" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
+        <v>資誠聯合會計師事務所</v>
+      </c>
+      <c r="C131" s="3"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0849")</f>
+        <v>A0849</v>
+      </c>
+      <c r="B132" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"遠邦國際品牌CrossBond")</f>
+        <v>遠邦國際品牌CrossBond</v>
+      </c>
+      <c r="C132" s="3"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0855")</f>
+        <v>A0855</v>
+      </c>
+      <c r="B133" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"StarFab (豪覓管理顧問股份有限公司)")</f>
+        <v>StarFab (豪覓管理顧問股份有限公司)</v>
+      </c>
+      <c r="C133" s="3"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0856")</f>
+        <v>A0856</v>
+      </c>
+      <c r="B134" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
+        <v>好食好事加速器</v>
+      </c>
+      <c r="C134" s="3"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0858")</f>
+        <v>A0858</v>
+      </c>
+      <c r="B135" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Garage+")</f>
+        <v>Garage+</v>
+      </c>
+      <c r="C135" s="3"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0864")</f>
+        <v>A0864</v>
+      </c>
+      <c r="B136" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資育股份有限公司")</f>
         <v>資育股份有限公司</v>
       </c>
-      <c r="C126" s="3"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0801")</f>
-        <v>A0801</v>
-      </c>
-      <c r="B127" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C127" s="3"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0808")</f>
-        <v>A0808</v>
-      </c>
-      <c r="B128" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C128" s="3"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0814")</f>
-        <v>A0814</v>
-      </c>
-      <c r="B129" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
-        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
-      </c>
-      <c r="C129" s="3"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0815")</f>
-        <v>A0815</v>
-      </c>
-      <c r="B130" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
-        <v>好食好事加速器</v>
-      </c>
-      <c r="C130" s="3"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0833")</f>
-        <v>A0833</v>
-      </c>
-      <c r="B131" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C131" s="3"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0838")</f>
-        <v>A0838</v>
-      </c>
-      <c r="B132" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
-        <v>資誠聯合會計師事務所</v>
-      </c>
-      <c r="C132" s="3"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0849")</f>
-        <v>A0849</v>
-      </c>
-      <c r="B133" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"遠邦國際品牌CrossBond")</f>
-        <v>遠邦國際品牌CrossBond</v>
-      </c>
-      <c r="C133" s="3"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0855")</f>
-        <v>A0855</v>
-      </c>
-      <c r="B134" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"StarFab (豪覓管理顧問股份有限公司)")</f>
-        <v>StarFab (豪覓管理顧問股份有限公司)</v>
-      </c>
-      <c r="C134" s="3"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0856")</f>
-        <v>A0856</v>
-      </c>
-      <c r="B135" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C135" s="3"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0858")</f>
-        <v>A0858</v>
-      </c>
-      <c r="B136" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Garage+")</f>
-        <v>Garage+</v>
-      </c>
       <c r="C136" s="3"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0864")</f>
-        <v>A0864</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0866")</f>
+        <v>A0866</v>
       </c>
       <c r="B137" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
@@ -1805,140 +1793,140 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0866")</f>
-        <v>A0866</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0872")</f>
+        <v>A0872</v>
       </c>
       <c r="B138" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"扶田資本股份有限公司")</f>
+        <v>扶田資本股份有限公司</v>
+      </c>
+      <c r="C138" s="3"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0880")</f>
+        <v>A0880</v>
+      </c>
+      <c r="B139" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
+        <v>聯合創新加速器</v>
+      </c>
+      <c r="C139" s="3"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0886")</f>
+        <v>A0886</v>
+      </c>
+      <c r="B140" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"安永聯合會計師事務所")</f>
+        <v>安永聯合會計師事務所</v>
+      </c>
+      <c r="C140" s="3"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0892")</f>
+        <v>A0892</v>
+      </c>
+      <c r="B141" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"台灣智慧雲端服務股份有限公司（台智雲）")</f>
+        <v>台灣智慧雲端服務股份有限公司（台智雲）</v>
+      </c>
+      <c r="C141" s="3"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0896")</f>
+        <v>A0896</v>
+      </c>
+      <c r="B142" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Muse Builder")</f>
+        <v>Muse Builder</v>
+      </c>
+      <c r="C142" s="3"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0905")</f>
+        <v>A0905</v>
+      </c>
+      <c r="B143" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
         <v>尚未報名/媒合中</v>
       </c>
-      <c r="C138" s="3"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0872")</f>
-        <v>A0872</v>
-      </c>
-      <c r="B139" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"扶田資本股份有限公司")</f>
-        <v>扶田資本股份有限公司</v>
-      </c>
-      <c r="C139" s="3"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0880")</f>
-        <v>A0880</v>
-      </c>
-      <c r="B140" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
-        <v>聯合創新加速器</v>
-      </c>
-      <c r="C140" s="3"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0886")</f>
-        <v>A0886</v>
-      </c>
-      <c r="B141" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"安永聯合會計師事務所")</f>
-        <v>安永聯合會計師事務所</v>
-      </c>
-      <c r="C141" s="3"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0892")</f>
-        <v>A0892</v>
-      </c>
-      <c r="B142" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"台灣智慧雲端服務股份有限公司（台智雲）")</f>
-        <v>台灣智慧雲端服務股份有限公司（台智雲）</v>
-      </c>
-      <c r="C142" s="3"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0896")</f>
-        <v>A0896</v>
-      </c>
-      <c r="B143" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Muse Builder")</f>
-        <v>Muse Builder</v>
-      </c>
       <c r="C143" s="3"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0905")</f>
-        <v>A0905</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0907")</f>
+        <v>A0907</v>
       </c>
       <c r="B144" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C144" s="3"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0921")</f>
+        <v>A0921</v>
+      </c>
+      <c r="B145" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
+        <v>好食好事加速器</v>
+      </c>
+      <c r="C145" s="3"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0927")</f>
+        <v>A0927</v>
+      </c>
+      <c r="B146" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
         <v>尚未報名/媒合中</v>
       </c>
-      <c r="C144" s="3"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0907")</f>
-        <v>A0907</v>
-      </c>
-      <c r="B145" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
-        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
-      </c>
-      <c r="C145" s="3"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0921")</f>
-        <v>A0921</v>
-      </c>
-      <c r="B146" s="3" t="str">
+      <c r="C146" s="3"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0943")</f>
+        <v>A0943</v>
+      </c>
+      <c r="B147" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
         <v>好食好事加速器</v>
       </c>
-      <c r="C146" s="3"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0927")</f>
-        <v>A0927</v>
-      </c>
-      <c r="B147" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
       <c r="C147" s="3"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0943")</f>
-        <v>A0943</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0964")</f>
+        <v>A0964</v>
       </c>
       <c r="B148" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
-        <v>好食好事加速器</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
       </c>
       <c r="C148" s="3"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0964")</f>
-        <v>A0964</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0972")</f>
+        <v>A0972</v>
       </c>
       <c r="B149" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
-        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"生物技術開發中心(南港生技育成中心)")</f>
+        <v>生物技術開發中心(南港生技育成中心)</v>
       </c>
       <c r="C149" s="3"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0972")</f>
-        <v>A0972</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0973")</f>
+        <v>A0973</v>
       </c>
       <c r="B150" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
@@ -1948,19 +1936,16 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0973")</f>
-        <v>A0973</v>
-      </c>
-      <c r="B151" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0997")</f>
+        <v>A0997</v>
+      </c>
+      <c r="B151" s="3"/>
       <c r="C151" s="3"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A0997")</f>
-        <v>A0997</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1012")</f>
+        <v>A1012</v>
       </c>
       <c r="B152" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
@@ -1970,261 +1955,261 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1012")</f>
-        <v>A1012</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1018")</f>
+        <v>A1018</v>
       </c>
       <c r="B153" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mighty Net(邁特創新基地)")</f>
+        <v>Mighty Net(邁特創新基地)</v>
+      </c>
+      <c r="C153" s="3"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1020")</f>
+        <v>A1020</v>
+      </c>
+      <c r="B154" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C154" s="3"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1022")</f>
+        <v>A1022</v>
+      </c>
+      <c r="B155" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Muse Builder")</f>
+        <v>Muse Builder</v>
+      </c>
+      <c r="C155" s="3"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1023")</f>
+        <v>A1023</v>
+      </c>
+      <c r="B156" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"StarFab (豪覓管理顧問股份有限公司)")</f>
+        <v>StarFab (豪覓管理顧問股份有限公司)</v>
+      </c>
+      <c r="C156" s="3"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1024")</f>
+        <v>A1024</v>
+      </c>
+      <c r="B157" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
         <v>尚未報名/媒合中</v>
       </c>
-      <c r="C153" s="3"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1018")</f>
-        <v>A1018</v>
-      </c>
-      <c r="B154" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mighty Net(邁特創新基地)")</f>
-        <v>Mighty Net(邁特創新基地)</v>
-      </c>
-      <c r="C154" s="3"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1020")</f>
-        <v>A1020</v>
-      </c>
-      <c r="B155" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
-        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
-      </c>
-      <c r="C155" s="3"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1022")</f>
-        <v>A1022</v>
-      </c>
-      <c r="B156" s="3" t="str">
+      <c r="C157" s="3"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1026")</f>
+        <v>A1026</v>
+      </c>
+      <c r="B158" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
+        <v>好食好事加速器</v>
+      </c>
+      <c r="C158" s="3"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1036")</f>
+        <v>A1036</v>
+      </c>
+      <c r="B159" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"扶田資本股份有限公司")</f>
+        <v>扶田資本股份有限公司</v>
+      </c>
+      <c r="C159" s="3"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1043")</f>
+        <v>A1043</v>
+      </c>
+      <c r="B160" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"國立陽明交通大學產業加速器暨專利開發策略中心")</f>
+        <v>國立陽明交通大學產業加速器暨專利開發策略中心</v>
+      </c>
+      <c r="C160" s="3"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1047")</f>
+        <v>A1047</v>
+      </c>
+      <c r="B161" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
         <v>尚未報名/媒合中</v>
       </c>
-      <c r="C156" s="3"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1023")</f>
-        <v>A1023</v>
-      </c>
-      <c r="B157" s="3" t="str">
+      <c r="C161" s="3"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1054")</f>
+        <v>A1054</v>
+      </c>
+      <c r="B162" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
+        <v>好食好事加速器</v>
+      </c>
+      <c r="C162" s="3"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1059")</f>
+        <v>A1059</v>
+      </c>
+      <c r="B163" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C163" s="3"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1061")</f>
+        <v>A1061</v>
+      </c>
+      <c r="B164" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
+        <v>資誠聯合會計師事務所</v>
+      </c>
+      <c r="C164" s="3"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1064")</f>
+        <v>A1064</v>
+      </c>
+      <c r="B165" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"StarFab (豪覓管理顧問股份有限公司)")</f>
         <v>StarFab (豪覓管理顧問股份有限公司)</v>
       </c>
-      <c r="C157" s="3"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1024")</f>
-        <v>A1024</v>
-      </c>
-      <c r="B158" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C158" s="3"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1026")</f>
-        <v>A1026</v>
-      </c>
-      <c r="B159" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C159" s="3"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1036")</f>
-        <v>A1036</v>
-      </c>
-      <c r="B160" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"扶田資本股份有限公司")</f>
-        <v>扶田資本股份有限公司</v>
-      </c>
-      <c r="C160" s="3"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1043")</f>
-        <v>A1043</v>
-      </c>
-      <c r="B161" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"國立陽明交通大學產業加速器暨專利開發策略中心")</f>
-        <v>國立陽明交通大學產業加速器暨專利開發策略中心</v>
-      </c>
-      <c r="C161" s="3"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1047")</f>
-        <v>A1047</v>
-      </c>
-      <c r="B162" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C162" s="3"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1054")</f>
-        <v>A1054</v>
-      </c>
-      <c r="B163" s="3" t="str">
+      <c r="C165" s="3"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1077")</f>
+        <v>A1077</v>
+      </c>
+      <c r="B166" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"活水影響力投資")</f>
+        <v>活水影響力投資</v>
+      </c>
+      <c r="C166" s="3"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1081")</f>
+        <v>A1081</v>
+      </c>
+      <c r="B167" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
+        <v>聯合創新加速器</v>
+      </c>
+      <c r="C167" s="3"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1090")</f>
+        <v>A1090</v>
+      </c>
+      <c r="B168" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"StarFab (豪覓管理顧問股份有限公司)")</f>
+        <v>StarFab (豪覓管理顧問股份有限公司)</v>
+      </c>
+      <c r="C168" s="3"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1103")</f>
+        <v>A1103</v>
+      </c>
+      <c r="B169" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Muse Builder")</f>
+        <v>Muse Builder</v>
+      </c>
+      <c r="C169" s="3"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1104")</f>
+        <v>A1104</v>
+      </c>
+      <c r="B170" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
+        <v>聯合創新加速器</v>
+      </c>
+      <c r="C170" s="3"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1106")</f>
+        <v>A1106</v>
+      </c>
+      <c r="B171" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
         <v>好食好事加速器</v>
       </c>
-      <c r="C163" s="3"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1059")</f>
-        <v>A1059</v>
-      </c>
-      <c r="B164" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C164" s="3"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1061")</f>
-        <v>A1061</v>
-      </c>
-      <c r="B165" s="3" t="str">
+      <c r="C171" s="3"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1112")</f>
+        <v>A1112</v>
+      </c>
+      <c r="B172" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"安永聯合會計師事務所")</f>
+        <v>安永聯合會計師事務所</v>
+      </c>
+      <c r="C172" s="3"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1133")</f>
+        <v>A1133</v>
+      </c>
+      <c r="B173" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
+        <v>比翼生醫</v>
+      </c>
+      <c r="C173" s="3"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1134")</f>
+        <v>A1134</v>
+      </c>
+      <c r="B174" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"酷日國際有限公司")</f>
+        <v>酷日國際有限公司</v>
+      </c>
+      <c r="C174" s="3"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1136")</f>
+        <v>A1136</v>
+      </c>
+      <c r="B175" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
         <v>資誠聯合會計師事務所</v>
       </c>
-      <c r="C165" s="3"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1064")</f>
-        <v>A1064</v>
-      </c>
-      <c r="B166" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"StarFab (豪覓管理顧問股份有限公司)")</f>
-        <v>StarFab (豪覓管理顧問股份有限公司)</v>
-      </c>
-      <c r="C166" s="3"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1077")</f>
-        <v>A1077</v>
-      </c>
-      <c r="B167" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"活水影響力投資")</f>
-        <v>活水影響力投資</v>
-      </c>
-      <c r="C167" s="3"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1081")</f>
-        <v>A1081</v>
-      </c>
-      <c r="B168" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
-        <v>聯合創新加速器</v>
-      </c>
-      <c r="C168" s="3"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1090")</f>
-        <v>A1090</v>
-      </c>
-      <c r="B169" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C169" s="3"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1103")</f>
-        <v>A1103</v>
-      </c>
-      <c r="B170" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Muse Builder")</f>
-        <v>Muse Builder</v>
-      </c>
-      <c r="C170" s="3"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1104")</f>
-        <v>A1104</v>
-      </c>
-      <c r="B171" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
-        <v>聯合創新加速器</v>
-      </c>
-      <c r="C171" s="3"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1106")</f>
-        <v>A1106</v>
-      </c>
-      <c r="B172" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C172" s="3"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1112")</f>
-        <v>A1112</v>
-      </c>
-      <c r="B173" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"安永聯合會計師事務所")</f>
-        <v>安永聯合會計師事務所</v>
-      </c>
-      <c r="C173" s="3"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1133")</f>
-        <v>A1133</v>
-      </c>
-      <c r="B174" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
-        <v>比翼生醫</v>
-      </c>
-      <c r="C174" s="3"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1134")</f>
-        <v>A1134</v>
-      </c>
-      <c r="B175" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"酷日國際有限公司")</f>
-        <v>酷日國際有限公司</v>
-      </c>
       <c r="C175" s="3"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1136")</f>
-        <v>A1136</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1142")</f>
+        <v>A1142</v>
       </c>
       <c r="B176" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
@@ -2234,118 +2219,118 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1142")</f>
-        <v>A1142</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1157")</f>
+        <v>A1157</v>
       </c>
       <c r="B177" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
+        <v>聯合創新加速器</v>
+      </c>
+      <c r="C177" s="3"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1181")</f>
+        <v>A1181</v>
+      </c>
+      <c r="B178" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
         <v>尚未報名/媒合中</v>
       </c>
-      <c r="C177" s="3"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1157")</f>
-        <v>A1157</v>
-      </c>
-      <c r="B178" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
-        <v>聯合創新加速器</v>
-      </c>
       <c r="C178" s="3"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1181")</f>
-        <v>A1181</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1187")</f>
+        <v>A1187</v>
       </c>
       <c r="B179" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"酷日國際有限公司")</f>
+        <v>酷日國際有限公司</v>
       </c>
       <c r="C179" s="3"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1187")</f>
-        <v>A1187</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1192")</f>
+        <v>A1192</v>
       </c>
       <c r="B180" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
+        <v>比翼生醫</v>
+      </c>
+      <c r="C180" s="3"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1197")</f>
+        <v>A1197</v>
+      </c>
+      <c r="B181" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"國立陽明交通大學產業加速器暨專利開發策略中心")</f>
+        <v>國立陽明交通大學產業加速器暨專利開發策略中心</v>
+      </c>
+      <c r="C181" s="3"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1198")</f>
+        <v>A1198</v>
+      </c>
+      <c r="B182" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
+        <v>好食好事加速器</v>
+      </c>
+      <c r="C182" s="3"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1200")</f>
+        <v>A1200</v>
+      </c>
+      <c r="B183" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"國立陽明交通大學產業加速器暨專利開發策略中心")</f>
+        <v>國立陽明交通大學產業加速器暨專利開發策略中心</v>
+      </c>
+      <c r="C183" s="3"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1202")</f>
+        <v>A1202</v>
+      </c>
+      <c r="B184" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C184" s="3"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1219")</f>
+        <v>A1219</v>
+      </c>
+      <c r="B185" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"酷日國際有限公司")</f>
         <v>酷日國際有限公司</v>
       </c>
-      <c r="C180" s="3"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1192")</f>
-        <v>A1192</v>
-      </c>
-      <c r="B181" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C181" s="3"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1197")</f>
-        <v>A1197</v>
-      </c>
-      <c r="B182" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"國立陽明交通大學產業加速器暨專利開發策略中心")</f>
-        <v>國立陽明交通大學產業加速器暨專利開發策略中心</v>
-      </c>
-      <c r="C182" s="3"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1198")</f>
-        <v>A1198</v>
-      </c>
-      <c r="B183" s="3" t="str">
+      <c r="C185" s="3"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1220")</f>
+        <v>A1220</v>
+      </c>
+      <c r="B186" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
         <v>好食好事加速器</v>
       </c>
-      <c r="C183" s="3"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1200")</f>
-        <v>A1200</v>
-      </c>
-      <c r="B184" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"國立陽明交通大學產業加速器暨專利開發策略中心")</f>
-        <v>國立陽明交通大學產業加速器暨專利開發策略中心</v>
-      </c>
-      <c r="C184" s="3"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1202")</f>
-        <v>A1202</v>
-      </c>
-      <c r="B185" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
-        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
-      </c>
-      <c r="C185" s="3"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1219")</f>
-        <v>A1219</v>
-      </c>
-      <c r="B186" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"酷日國際有限公司")</f>
-        <v>酷日國際有限公司</v>
-      </c>
       <c r="C186" s="3"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1220")</f>
-        <v>A1220</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1228")</f>
+        <v>A1228</v>
       </c>
       <c r="B187" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
@@ -2355,8 +2340,8 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1228")</f>
-        <v>A1228</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1236")</f>
+        <v>A1236</v>
       </c>
       <c r="B188" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
@@ -2366,74 +2351,74 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1236")</f>
-        <v>A1236</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1257")</f>
+        <v>A1257</v>
       </c>
       <c r="B189" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
       </c>
       <c r="C189" s="3"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1257")</f>
-        <v>A1257</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1273")</f>
+        <v>A1273</v>
       </c>
       <c r="B190" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
-        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Muse Builder")</f>
+        <v>Muse Builder</v>
       </c>
       <c r="C190" s="3"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1273")</f>
-        <v>A1273</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1277")</f>
+        <v>A1277</v>
       </c>
       <c r="B191" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Muse Builder")</f>
-        <v>Muse Builder</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Garage+")</f>
+        <v>Garage+</v>
       </c>
       <c r="C191" s="3"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1277")</f>
-        <v>A1277</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1284")</f>
+        <v>A1284</v>
       </c>
       <c r="B192" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Garage+")</f>
-        <v>Garage+</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mosaic Venture Lab 宇斻管理顧問股份有限公司")</f>
+        <v>Mosaic Venture Lab 宇斻管理顧問股份有限公司</v>
       </c>
       <c r="C192" s="3"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1284")</f>
-        <v>A1284</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1301")</f>
+        <v>A1301</v>
       </c>
       <c r="B193" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mosaic Venture Lab 宇斻管理顧問股份有限公司")</f>
-        <v>Mosaic Venture Lab 宇斻管理顧問股份有限公司</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
       </c>
       <c r="C193" s="3"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1301")</f>
-        <v>A1301</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1313")</f>
+        <v>A1313</v>
       </c>
       <c r="B194" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
-        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
+        <v>資誠聯合會計師事務所</v>
       </c>
       <c r="C194" s="3"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1313")</f>
-        <v>A1313</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1326")</f>
+        <v>A1326</v>
       </c>
       <c r="B195" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
@@ -2443,41 +2428,41 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1326")</f>
-        <v>A1326</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1342")</f>
+        <v>A1342</v>
       </c>
       <c r="B196" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
+        <v>聯合創新加速器</v>
+      </c>
+      <c r="C196" s="3"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1343")</f>
+        <v>A1343</v>
+      </c>
+      <c r="B197" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Muse Builder")</f>
+        <v>Muse Builder</v>
+      </c>
+      <c r="C197" s="3"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1348")</f>
+        <v>A1348</v>
+      </c>
+      <c r="B198" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
         <v>尚未報名/媒合中</v>
       </c>
-      <c r="C196" s="3"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1342")</f>
-        <v>A1342</v>
-      </c>
-      <c r="B197" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
-        <v>聯合創新加速器</v>
-      </c>
-      <c r="C197" s="3"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1343")</f>
-        <v>A1343</v>
-      </c>
-      <c r="B198" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Muse Builder")</f>
-        <v>Muse Builder</v>
-      </c>
       <c r="C198" s="3"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1348")</f>
-        <v>A1348</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1355")</f>
+        <v>A1355</v>
       </c>
       <c r="B199" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
@@ -2487,8 +2472,8 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1355")</f>
-        <v>A1355</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1361")</f>
+        <v>A1361</v>
       </c>
       <c r="B200" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
@@ -2498,107 +2483,104 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1361")</f>
-        <v>A1361</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1367")</f>
+        <v>A1367</v>
       </c>
       <c r="B201" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
+        <v>資誠聯合會計師事務所</v>
       </c>
       <c r="C201" s="3"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1367")</f>
-        <v>A1367</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1377")</f>
+        <v>A1377</v>
       </c>
       <c r="B202" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
-        <v>資誠聯合會計師事務所</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"扶田資本股份有限公司")</f>
+        <v>扶田資本股份有限公司</v>
       </c>
       <c r="C202" s="3"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1377")</f>
-        <v>A1377</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1405")</f>
+        <v>A1405</v>
       </c>
       <c r="B203" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"扶田資本股份有限公司")</f>
-        <v>扶田資本股份有限公司</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
       </c>
       <c r="C203" s="3"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1405")</f>
-        <v>A1405</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1421")</f>
+        <v>A1421</v>
       </c>
       <c r="B204" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
-        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"酷日國際有限公司")</f>
+        <v>酷日國際有限公司</v>
       </c>
       <c r="C204" s="3"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1421")</f>
-        <v>A1421</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1464")</f>
+        <v>A1464</v>
       </c>
       <c r="B205" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"酷日國際有限公司")</f>
-        <v>酷日國際有限公司</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
       </c>
       <c r="C205" s="3"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1464")</f>
-        <v>A1464</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1491")</f>
+        <v>A1491</v>
       </c>
       <c r="B206" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
-        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"購威經濟股份有限公司(智慧高軟)")</f>
+        <v>購威經濟股份有限公司(智慧高軟)</v>
       </c>
       <c r="C206" s="3"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1491")</f>
-        <v>A1491</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1577")</f>
+        <v>A1577</v>
       </c>
       <c r="B207" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mosaic Venture Lab 宇斻管理顧問股份有限公司")</f>
+        <v>Mosaic Venture Lab 宇斻管理顧問股份有限公司</v>
       </c>
       <c r="C207" s="3"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1577")</f>
-        <v>A1577</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1579")</f>
+        <v>A1579</v>
       </c>
       <c r="B208" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"台灣智慧雲端服務股份有限公司（台智雲）")</f>
+        <v>台灣智慧雲端服務股份有限公司（台智雲）</v>
       </c>
       <c r="C208" s="3"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1579")</f>
-        <v>A1579</v>
-      </c>
-      <c r="B209" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"台灣智慧雲端服務股份有限公司（台智雲）")</f>
-        <v>台灣智慧雲端服務股份有限公司（台智雲）</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1590")</f>
+        <v>A1590</v>
+      </c>
+      <c r="B209" s="3"/>
       <c r="C209" s="3"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1590")</f>
-        <v>A1590</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1631")</f>
+        <v>A1631</v>
       </c>
       <c r="B210" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
@@ -2608,217 +2590,214 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A1631")</f>
-        <v>A1631</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0012")</f>
+        <v>B0012</v>
       </c>
       <c r="B211" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"扶田資本股份有限公司")</f>
+        <v>扶田資本股份有限公司</v>
       </c>
       <c r="C211" s="3"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0012")</f>
-        <v>B0012</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0016")</f>
+        <v>B0016</v>
       </c>
       <c r="B212" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
       </c>
       <c r="C212" s="3"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0016")</f>
-        <v>B0016</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0019")</f>
+        <v>B0019</v>
       </c>
       <c r="B213" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Muse Builder")</f>
+        <v>Muse Builder</v>
       </c>
       <c r="C213" s="3"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0019")</f>
-        <v>B0019</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0050")</f>
+        <v>B0050</v>
       </c>
       <c r="B214" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"StarFab (豪覓管理顧問股份有限公司)")</f>
+        <v>StarFab (豪覓管理顧問股份有限公司)</v>
+      </c>
+      <c r="C214" s="3"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0055")</f>
+        <v>B0055</v>
+      </c>
+      <c r="B215" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Garage+")</f>
+        <v>Garage+</v>
+      </c>
+      <c r="C215" s="3"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0082")</f>
+        <v>B0082</v>
+      </c>
+      <c r="B216" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Muse Builder")</f>
         <v>Muse Builder</v>
       </c>
-      <c r="C214" s="3"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0050")</f>
-        <v>B0050</v>
-      </c>
-      <c r="B215" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"StarFab (豪覓管理顧問股份有限公司)")</f>
-        <v>StarFab (豪覓管理顧問股份有限公司)</v>
-      </c>
-      <c r="C215" s="3"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0055")</f>
-        <v>B0055</v>
-      </c>
-      <c r="B216" s="3" t="str">
+      <c r="C216" s="3"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0136")</f>
+        <v>B0136</v>
+      </c>
+      <c r="B217" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"台灣智慧雲端服務股份有限公司（台智雲）")</f>
+        <v>台灣智慧雲端服務股份有限公司（台智雲）</v>
+      </c>
+      <c r="C217" s="3"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0140")</f>
+        <v>B0140</v>
+      </c>
+      <c r="B218" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C218" s="3"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0144")</f>
+        <v>B0144</v>
+      </c>
+      <c r="B219" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
+        <v>比翼生醫</v>
+      </c>
+      <c r="C219" s="3"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0152")</f>
+        <v>B0152</v>
+      </c>
+      <c r="B220" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
+        <v>聯合創新加速器</v>
+      </c>
+      <c r="C220" s="3"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0167")</f>
+        <v>B0167</v>
+      </c>
+      <c r="B221" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
+        <v>資誠聯合會計師事務所</v>
+      </c>
+      <c r="C221" s="3"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0179")</f>
+        <v>B0179</v>
+      </c>
+      <c r="B222" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Garage+")</f>
         <v>Garage+</v>
       </c>
-      <c r="C216" s="3"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0082")</f>
-        <v>B0082</v>
-      </c>
-      <c r="B217" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C217" s="3"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0136")</f>
-        <v>B0136</v>
-      </c>
-      <c r="B218" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"台灣智慧雲端服務股份有限公司（台智雲）")</f>
-        <v>台灣智慧雲端服務股份有限公司（台智雲）</v>
-      </c>
-      <c r="C218" s="3"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0140")</f>
-        <v>B0140</v>
-      </c>
-      <c r="B219" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C219" s="3"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0144")</f>
-        <v>B0144</v>
-      </c>
-      <c r="B220" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C220" s="3"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0152")</f>
-        <v>B0152</v>
-      </c>
-      <c r="B221" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
-        <v>聯合創新加速器</v>
-      </c>
-      <c r="C221" s="3"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0167")</f>
-        <v>B0167</v>
-      </c>
-      <c r="B222" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
       <c r="C222" s="3"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0179")</f>
-        <v>B0179</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0182")</f>
+        <v>B0182</v>
       </c>
       <c r="B223" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
+        <v>比翼生醫</v>
       </c>
       <c r="C223" s="3"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0182")</f>
-        <v>B0182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0185")</f>
+        <v>B0185</v>
       </c>
       <c r="B224" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"國立陽明交通大學產業加速器暨專利開發策略中心")</f>
+        <v>國立陽明交通大學產業加速器暨專利開發策略中心</v>
       </c>
       <c r="C224" s="3"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0185")</f>
-        <v>B0185</v>
-      </c>
-      <c r="B225" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0190")</f>
+        <v>B0190</v>
+      </c>
+      <c r="B225" s="3"/>
       <c r="C225" s="3"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0190")</f>
-        <v>B0190</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0208")</f>
+        <v>B0208</v>
       </c>
       <c r="B226" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"國家衛生研究院/ 創新育成中心")</f>
+        <v>國家衛生研究院/ 創新育成中心</v>
       </c>
       <c r="C226" s="3"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0208")</f>
-        <v>B0208</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0222")</f>
+        <v>B0222</v>
       </c>
       <c r="B227" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資育股份有限公司")</f>
+        <v>資育股份有限公司</v>
+      </c>
+      <c r="C227" s="3"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0233")</f>
+        <v>B0233</v>
+      </c>
+      <c r="B228" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"國家衛生研究院/ 創新育成中心")</f>
         <v>國家衛生研究院/ 創新育成中心</v>
       </c>
-      <c r="C227" s="3"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0222")</f>
-        <v>B0222</v>
-      </c>
-      <c r="B228" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
       <c r="C228" s="3"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0233")</f>
-        <v>B0233</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0253")</f>
+        <v>B0253</v>
       </c>
       <c r="B229" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
+        <v>比翼生醫</v>
       </c>
       <c r="C229" s="3"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0253")</f>
-        <v>B0253</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0259")</f>
+        <v>B0259</v>
       </c>
       <c r="B230" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
@@ -2828,63 +2807,63 @@
     </row>
     <row r="231">
       <c r="A231" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0259")</f>
-        <v>B0259</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0274")</f>
+        <v>B0274</v>
       </c>
       <c r="B231" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
       </c>
       <c r="C231" s="3"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0274")</f>
-        <v>B0274</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0305")</f>
+        <v>B0305</v>
       </c>
       <c r="B232" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
+        <v>好食好事加速器</v>
       </c>
       <c r="C232" s="3"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0305")</f>
-        <v>B0305</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0321")</f>
+        <v>B0321</v>
       </c>
       <c r="B233" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
-        <v>好食好事加速器</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"安永聯合會計師事務所")</f>
+        <v>安永聯合會計師事務所</v>
       </c>
       <c r="C233" s="3"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0321")</f>
-        <v>B0321</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0344")</f>
+        <v>B0344</v>
       </c>
       <c r="B234" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"購威經濟股份有限公司(智慧高軟)")</f>
+        <v>購威經濟股份有限公司(智慧高軟)</v>
       </c>
       <c r="C234" s="3"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0344")</f>
-        <v>B0344</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0354")</f>
+        <v>B0354</v>
       </c>
       <c r="B235" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"購威經濟股份有限公司(智慧高軟)")</f>
-        <v>購威經濟股份有限公司(智慧高軟)</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
+        <v>比翼生醫</v>
       </c>
       <c r="C235" s="3"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0354")</f>
-        <v>B0354</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0369")</f>
+        <v>B0369</v>
       </c>
       <c r="B236" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
@@ -2894,118 +2873,118 @@
     </row>
     <row r="237">
       <c r="A237" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0369")</f>
-        <v>B0369</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0398")</f>
+        <v>B0398</v>
       </c>
       <c r="B237" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"博大國際智權股份有限公司")</f>
+        <v>博大國際智權股份有限公司</v>
       </c>
       <c r="C237" s="3"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0398")</f>
-        <v>B0398</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0399")</f>
+        <v>B0399</v>
       </c>
       <c r="B238" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"博大國際智權股份有限公司")</f>
-        <v>博大國際智權股份有限公司</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"國家衛生研究院/ 創新育成中心")</f>
+        <v>國家衛生研究院/ 創新育成中心</v>
       </c>
       <c r="C238" s="3"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0399")</f>
-        <v>B0399</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0400")</f>
+        <v>B0400</v>
       </c>
       <c r="B239" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"國家衛生研究院/ 創新育成中心")</f>
-        <v>國家衛生研究院/ 創新育成中心</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
       </c>
       <c r="C239" s="3"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0400")</f>
-        <v>B0400</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0402")</f>
+        <v>B0402</v>
       </c>
       <c r="B240" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
-        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Muse Builder")</f>
+        <v>Muse Builder</v>
       </c>
       <c r="C240" s="3"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0402")</f>
-        <v>B0402</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0442")</f>
+        <v>B0442</v>
       </c>
       <c r="B241" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
+        <v>聯合創新加速器</v>
       </c>
       <c r="C241" s="3"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0442")</f>
-        <v>B0442</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0446")</f>
+        <v>B0446</v>
       </c>
       <c r="B242" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
       </c>
       <c r="C242" s="3"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0446")</f>
-        <v>B0446</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0455")</f>
+        <v>B0455</v>
       </c>
       <c r="B243" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
-        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
+        <v>比翼生醫</v>
       </c>
       <c r="C243" s="3"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0455")</f>
-        <v>B0455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0462")</f>
+        <v>B0462</v>
       </c>
       <c r="B244" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mosaic Venture Lab 宇斻管理顧問股份有限公司")</f>
+        <v>Mosaic Venture Lab 宇斻管理顧問股份有限公司</v>
       </c>
       <c r="C244" s="3"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0462")</f>
-        <v>B0462</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0467")</f>
+        <v>B0467</v>
       </c>
       <c r="B245" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
       </c>
       <c r="C245" s="3"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0467")</f>
-        <v>B0467</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0479")</f>
+        <v>B0479</v>
       </c>
       <c r="B246" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
       </c>
       <c r="C246" s="3"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0479")</f>
-        <v>B0479</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0482")</f>
+        <v>B0482</v>
       </c>
       <c r="B247" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
@@ -3015,52 +2994,52 @@
     </row>
     <row r="248">
       <c r="A248" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0482")</f>
-        <v>B0482</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0485")</f>
+        <v>B0485</v>
       </c>
       <c r="B248" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
       </c>
       <c r="C248" s="3"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0485")</f>
-        <v>B0485</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0486")</f>
+        <v>B0486</v>
       </c>
       <c r="B249" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Garage+")</f>
+        <v>Garage+</v>
       </c>
       <c r="C249" s="3"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0486")</f>
-        <v>B0486</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0490")</f>
+        <v>B0490</v>
       </c>
       <c r="B250" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"遠邦國際品牌CrossBond")</f>
+        <v>遠邦國際品牌CrossBond</v>
       </c>
       <c r="C250" s="3"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0490")</f>
-        <v>B0490</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0492")</f>
+        <v>B0492</v>
       </c>
       <c r="B251" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Garage+")</f>
+        <v>Garage+</v>
       </c>
       <c r="C251" s="3"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0492")</f>
-        <v>B0492</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0517")</f>
+        <v>B0517</v>
       </c>
       <c r="B252" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
@@ -3070,19 +3049,19 @@
     </row>
     <row r="253">
       <c r="A253" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0517")</f>
-        <v>B0517</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0533")</f>
+        <v>B0533</v>
       </c>
       <c r="B253" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
       </c>
       <c r="C253" s="3"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0533")</f>
-        <v>B0533</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0534")</f>
+        <v>B0534</v>
       </c>
       <c r="B254" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
@@ -3092,140 +3071,140 @@
     </row>
     <row r="255">
       <c r="A255" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0534")</f>
-        <v>B0534</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0535")</f>
+        <v>B0535</v>
       </c>
       <c r="B255" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
+        <v>聯合創新加速器</v>
+      </c>
+      <c r="C255" s="3"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0536")</f>
+        <v>B0536</v>
+      </c>
+      <c r="B256" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
+        <v>比翼生醫</v>
+      </c>
+      <c r="C256" s="3"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0540")</f>
+        <v>B0540</v>
+      </c>
+      <c r="B257" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
+        <v>資誠聯合會計師事務所</v>
+      </c>
+      <c r="C257" s="3"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0565")</f>
+        <v>B0565</v>
+      </c>
+      <c r="B258" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"安永聯合會計師事務所")</f>
+        <v>安永聯合會計師事務所</v>
+      </c>
+      <c r="C258" s="3"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0567")</f>
+        <v>B0567</v>
+      </c>
+      <c r="B259" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C259" s="3"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0583")</f>
+        <v>B0583</v>
+      </c>
+      <c r="B260" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
         <v>尚未報名/媒合中</v>
       </c>
-      <c r="C255" s="3"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0535")</f>
-        <v>B0535</v>
-      </c>
-      <c r="B256" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
-        <v>聯合創新加速器</v>
-      </c>
-      <c r="C256" s="3"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0536")</f>
-        <v>B0536</v>
-      </c>
-      <c r="B257" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C257" s="3"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0540")</f>
-        <v>B0540</v>
-      </c>
-      <c r="B258" s="3" t="str">
+      <c r="C260" s="3"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0604")</f>
+        <v>B0604</v>
+      </c>
+      <c r="B261" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
         <v>資誠聯合會計師事務所</v>
       </c>
-      <c r="C258" s="3"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0565")</f>
-        <v>B0565</v>
-      </c>
-      <c r="B259" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"安永聯合會計師事務所")</f>
-        <v>安永聯合會計師事務所</v>
-      </c>
-      <c r="C259" s="3"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0567")</f>
-        <v>B0567</v>
-      </c>
-      <c r="B260" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
-        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
-      </c>
-      <c r="C260" s="3"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0583")</f>
-        <v>B0583</v>
-      </c>
-      <c r="B261" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
       <c r="C261" s="3"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0604")</f>
-        <v>B0604</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0606")</f>
+        <v>B0606</v>
       </c>
       <c r="B262" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
       </c>
       <c r="C262" s="3"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0606")</f>
-        <v>B0606</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0607")</f>
+        <v>B0607</v>
       </c>
       <c r="B263" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
-        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"扶田資本股份有限公司")</f>
+        <v>扶田資本股份有限公司</v>
       </c>
       <c r="C263" s="3"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0607")</f>
-        <v>B0607</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0618")</f>
+        <v>B0618</v>
       </c>
       <c r="B264" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
+        <v>好食好事加速器</v>
       </c>
       <c r="C264" s="3"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0618")</f>
-        <v>B0618</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0619")</f>
+        <v>B0619</v>
       </c>
       <c r="B265" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
-        <v>好食好事加速器</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"酷日國際有限公司")</f>
+        <v>酷日國際有限公司</v>
       </c>
       <c r="C265" s="3"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0619")</f>
-        <v>B0619</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0651")</f>
+        <v>B0651</v>
       </c>
       <c r="B266" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"酷日國際有限公司")</f>
-        <v>酷日國際有限公司</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"台灣智慧雲端服務股份有限公司（台智雲）")</f>
+        <v>台灣智慧雲端服務股份有限公司（台智雲）</v>
       </c>
       <c r="C266" s="3"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0651")</f>
-        <v>B0651</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0652")</f>
+        <v>B0652</v>
       </c>
       <c r="B267" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
@@ -3235,239 +3214,230 @@
     </row>
     <row r="268">
       <c r="A268" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0652")</f>
-        <v>B0652</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0653")</f>
+        <v>B0653</v>
       </c>
       <c r="B268" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
       </c>
       <c r="C268" s="3"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0653")</f>
-        <v>B0653</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0672")</f>
+        <v>B0672</v>
       </c>
       <c r="B269" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"台灣智慧雲端服務股份有限公司（台智雲）")</f>
+        <v>台灣智慧雲端服務股份有限公司（台智雲）</v>
       </c>
       <c r="C269" s="3"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0672")</f>
-        <v>B0672</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0679")</f>
+        <v>B0679</v>
       </c>
       <c r="B270" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Garage+")</f>
+        <v>Garage+</v>
+      </c>
+      <c r="C270" s="3"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0703")</f>
+        <v>B0703</v>
+      </c>
+      <c r="B271" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C271" s="3"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0709")</f>
+        <v>B0709</v>
+      </c>
+      <c r="B272" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"安永聯合會計師事務所")</f>
+        <v>安永聯合會計師事務所</v>
+      </c>
+      <c r="C272" s="3"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0718")</f>
+        <v>B0718</v>
+      </c>
+      <c r="B273" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"遠邦國際品牌CrossBond")</f>
+        <v>遠邦國際品牌CrossBond</v>
+      </c>
+      <c r="C273" s="3"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0735")</f>
+        <v>B0735</v>
+      </c>
+      <c r="B274" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mighty Net(邁特創新基地)")</f>
+        <v>Mighty Net(邁特創新基地)</v>
+      </c>
+      <c r="C274" s="3"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0768")</f>
+        <v>B0768</v>
+      </c>
+      <c r="B275" s="3"/>
+      <c r="C275" s="3"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0788")</f>
+        <v>B0788</v>
+      </c>
+      <c r="B276" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
+        <v>聯合創新加速器</v>
+      </c>
+      <c r="C276" s="3"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0824")</f>
+        <v>B0824</v>
+      </c>
+      <c r="B277" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
+        <v>好食好事加速器</v>
+      </c>
+      <c r="C277" s="3"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0852")</f>
+        <v>B0852</v>
+      </c>
+      <c r="B278" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
+        <v>好食好事加速器</v>
+      </c>
+      <c r="C278" s="3"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0901")</f>
+        <v>B0901</v>
+      </c>
+      <c r="B279" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"台灣智慧雲端服務股份有限公司（台智雲）")</f>
         <v>台灣智慧雲端服務股份有限公司（台智雲）</v>
       </c>
-      <c r="C270" s="3"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0679")</f>
-        <v>B0679</v>
-      </c>
-      <c r="B271" s="3" t="str">
+      <c r="C279" s="3"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0905")</f>
+        <v>B0905</v>
+      </c>
+      <c r="B280" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"安永聯合會計師事務所")</f>
+        <v>安永聯合會計師事務所</v>
+      </c>
+      <c r="C280" s="3"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0911")</f>
+        <v>B0911</v>
+      </c>
+      <c r="B281" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
+        <v>比翼生醫</v>
+      </c>
+      <c r="C281" s="3"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0914")</f>
+        <v>B0914</v>
+      </c>
+      <c r="B282" s="3"/>
+      <c r="C282" s="3"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0926")</f>
+        <v>B0926</v>
+      </c>
+      <c r="B283" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C283" s="3"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0935")</f>
+        <v>B0935</v>
+      </c>
+      <c r="B284" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
+        <v>比翼生醫</v>
+      </c>
+      <c r="C284" s="3"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0943")</f>
+        <v>B0943</v>
+      </c>
+      <c r="B285" s="3"/>
+      <c r="C285" s="3"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0962")</f>
+        <v>B0962</v>
+      </c>
+      <c r="B286" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
+        <v>資誠聯合會計師事務所</v>
+      </c>
+      <c r="C286" s="3"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0973")</f>
+        <v>B0973</v>
+      </c>
+      <c r="B287" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C287" s="3"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0976")</f>
+        <v>B0976</v>
+      </c>
+      <c r="B288" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Garage+")</f>
         <v>Garage+</v>
       </c>
-      <c r="C271" s="3"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0703")</f>
-        <v>B0703</v>
-      </c>
-      <c r="B272" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C272" s="3"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0709")</f>
-        <v>B0709</v>
-      </c>
-      <c r="B273" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C273" s="3"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0718")</f>
-        <v>B0718</v>
-      </c>
-      <c r="B274" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C274" s="3"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0735")</f>
-        <v>B0735</v>
-      </c>
-      <c r="B275" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mighty Net(邁特創新基地)")</f>
-        <v>Mighty Net(邁特創新基地)</v>
-      </c>
-      <c r="C275" s="3"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0768")</f>
-        <v>B0768</v>
-      </c>
-      <c r="B276" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C276" s="3"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0788")</f>
-        <v>B0788</v>
-      </c>
-      <c r="B277" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"聯合創新加速器")</f>
-        <v>聯合創新加速器</v>
-      </c>
-      <c r="C277" s="3"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0824")</f>
-        <v>B0824</v>
-      </c>
-      <c r="B278" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C278" s="3"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0852")</f>
-        <v>B0852</v>
-      </c>
-      <c r="B279" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C279" s="3"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0901")</f>
-        <v>B0901</v>
-      </c>
-      <c r="B280" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C280" s="3"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0905")</f>
-        <v>B0905</v>
-      </c>
-      <c r="B281" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C281" s="3"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0911")</f>
-        <v>B0911</v>
-      </c>
-      <c r="B282" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"比翼生醫")</f>
-        <v>比翼生醫</v>
-      </c>
-      <c r="C282" s="3"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0914")</f>
-        <v>B0914</v>
-      </c>
-      <c r="B283" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C283" s="3"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0926")</f>
-        <v>B0926</v>
-      </c>
-      <c r="B284" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C284" s="3"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0935")</f>
-        <v>B0935</v>
-      </c>
-      <c r="B285" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C285" s="3"/>
-    </row>
-    <row r="286">
-      <c r="A286" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0943")</f>
-        <v>B0943</v>
-      </c>
-      <c r="B286" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C286" s="3"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0962")</f>
-        <v>B0962</v>
-      </c>
-      <c r="B287" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"資誠聯合會計師事務所")</f>
-        <v>資誠聯合會計師事務所</v>
-      </c>
-      <c r="C287" s="3"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0973")</f>
-        <v>B0973</v>
-      </c>
-      <c r="B288" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
       <c r="C288" s="3"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B0976")</f>
-        <v>B0976</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1009")</f>
+        <v>B1009</v>
       </c>
       <c r="B289" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Garage+")</f>
@@ -3477,145 +3447,136 @@
     </row>
     <row r="290">
       <c r="A290" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1009")</f>
-        <v>B1009</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1021")</f>
+        <v>B1021</v>
       </c>
       <c r="B290" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
+        <v>好食好事加速器</v>
+      </c>
+      <c r="C290" s="3"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1053")</f>
+        <v>B1053</v>
+      </c>
+      <c r="B291" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"國家衛生研究院/ 創新育成中心")</f>
+        <v>國家衛生研究院/ 創新育成中心</v>
+      </c>
+      <c r="C291" s="3"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1063")</f>
+        <v>B1063</v>
+      </c>
+      <c r="B292" s="3"/>
+      <c r="C292" s="3"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1085")</f>
+        <v>B1085</v>
+      </c>
+      <c r="B293" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C293" s="3"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1102")</f>
+        <v>B1102</v>
+      </c>
+      <c r="B294" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C294" s="3"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1120")</f>
+        <v>B1120</v>
+      </c>
+      <c r="B295" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Garage+")</f>
+        <v>Garage+</v>
+      </c>
+      <c r="C295" s="3"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1133")</f>
+        <v>B1133</v>
+      </c>
+      <c r="B296" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"StarFab (豪覓管理顧問股份有限公司)")</f>
+        <v>StarFab (豪覓管理顧問股份有限公司)</v>
+      </c>
+      <c r="C296" s="3"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1189")</f>
+        <v>B1189</v>
+      </c>
+      <c r="B297" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SparkLabs Taiwan 斯伯克國際創業投資有限公司")</f>
+        <v>SparkLabs Taiwan 斯伯克國際創業投資有限公司</v>
+      </c>
+      <c r="C297" s="3"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1196")</f>
+        <v>B1196</v>
+      </c>
+      <c r="B298" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"扶田資本股份有限公司")</f>
+        <v>扶田資本股份有限公司</v>
+      </c>
+      <c r="C298" s="3"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1203")</f>
+        <v>B1203</v>
+      </c>
+      <c r="B299" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
         <v>尚未報名/媒合中</v>
       </c>
-      <c r="C290" s="3"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1021")</f>
-        <v>B1021</v>
-      </c>
-      <c r="B291" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"好食好事加速器")</f>
-        <v>好食好事加速器</v>
-      </c>
-      <c r="C291" s="3"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1053")</f>
-        <v>B1053</v>
-      </c>
-      <c r="B292" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C292" s="3"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1063")</f>
-        <v>B1063</v>
-      </c>
-      <c r="B293" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C293" s="3"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1085")</f>
-        <v>B1085</v>
-      </c>
-      <c r="B294" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C294" s="3"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1102")</f>
-        <v>B1102</v>
-      </c>
-      <c r="B295" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C295" s="3"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1120")</f>
-        <v>B1120</v>
-      </c>
-      <c r="B296" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Garage+")</f>
-        <v>Garage+</v>
-      </c>
-      <c r="C296" s="3"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1133")</f>
-        <v>B1133</v>
-      </c>
-      <c r="B297" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"StarFab (豪覓管理顧問股份有限公司)")</f>
-        <v>StarFab (豪覓管理顧問股份有限公司)</v>
-      </c>
-      <c r="C297" s="3"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1189")</f>
-        <v>B1189</v>
-      </c>
-      <c r="B298" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
-      <c r="C298" s="3"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1196")</f>
-        <v>B1196</v>
-      </c>
-      <c r="B299" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"扶田資本股份有限公司")</f>
-        <v>扶田資本股份有限公司</v>
-      </c>
       <c r="C299" s="3"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1203")</f>
-        <v>B1203</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1207")</f>
+        <v>B1207</v>
       </c>
       <c r="B300" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"遠邦國際品牌CrossBond")</f>
+        <v>遠邦國際品牌CrossBond</v>
       </c>
       <c r="C300" s="3"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1207")</f>
-        <v>B1207</v>
-      </c>
-      <c r="B301" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"遠邦國際品牌CrossBond")</f>
-        <v>遠邦國際品牌CrossBond</v>
-      </c>
-      <c r="C301" s="3"/>
-    </row>
-    <row r="302">
-      <c r="A302" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B1255")</f>
         <v>B1255</v>
       </c>
-      <c r="B302" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"尚未報名/媒合中")</f>
-        <v>尚未報名/媒合中</v>
-      </c>
+      <c r="B301" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"酷日國際有限公司")</f>
+        <v>酷日國際有限公司</v>
+      </c>
+      <c r="C301" s="3"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="3"/>
+      <c r="B302" s="3"/>
       <c r="C302" s="3"/>
     </row>
   </sheetData>
